--- a/PCB/BOM BreaksRGB_PPU.xlsx
+++ b/PCB/BOM BreaksRGB_PPU.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="137">
   <si>
     <t>U3</t>
   </si>
@@ -156,9 +156,6 @@
     <t>R4,R5,R6,R9,R17,R25,R26,R27,R28</t>
   </si>
   <si>
-    <t>R29</t>
-  </si>
-  <si>
     <t>R30</t>
   </si>
   <si>
@@ -343,9 +340,6 @@
   </si>
   <si>
     <t xml:space="preserve">100Ω±5%   </t>
-  </si>
-  <si>
-    <t>RC0805JR-07110RL</t>
   </si>
   <si>
     <t>RC0805JR-07100RL</t>
@@ -443,6 +437,9 @@
   </si>
   <si>
     <t xml:space="preserve"> 74LVC1G04GV,125, nexperia. 1 Gate Schmitt trigger inverter or 1 Gate inverter</t>
+  </si>
+  <si>
+    <t>EP2C5T144I8N</t>
   </si>
 </sst>
 </file>
@@ -4590,7 +4587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:V50"/>
+  <dimension ref="A4:V49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -4625,25 +4622,25 @@
     </row>
     <row r="5" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C5" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
@@ -4660,7 +4657,7 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C6" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -4669,7 +4666,7 @@
         <v>6</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G6" s="33" t="s">
         <v>7</v>
@@ -4678,7 +4675,7 @@
         <v>6</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
@@ -4704,7 +4701,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>9</v>
@@ -4713,7 +4710,7 @@
         <v>8</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
@@ -4739,7 +4736,7 @@
         <v>10</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>11</v>
@@ -4748,7 +4745,7 @@
         <v>10</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
@@ -4774,7 +4771,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>13</v>
@@ -4795,7 +4792,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>15</v>
@@ -4814,19 +4811,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G11" s="32" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J11" s="7"/>
     </row>
@@ -4843,7 +4840,7 @@
         <v>17</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G12" s="31" t="s">
         <v>18</v>
@@ -4851,7 +4848,9 @@
       <c r="H12" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="21"/>
+      <c r="I12" s="21" t="s">
+        <v>136</v>
+      </c>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
@@ -4877,7 +4876,7 @@
         <v>22</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G13" s="30" t="s">
         <v>23</v>
@@ -4912,7 +4911,7 @@
         <v>24</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G14" s="32" t="s">
         <v>25</v>
@@ -4947,7 +4946,7 @@
         <v>26</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>25</v>
@@ -4979,17 +4978,17 @@
         <v>1</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G16" s="31" t="s">
         <v>30</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J16" s="9"/>
       <c r="K16" s="9"/>
@@ -5014,17 +5013,17 @@
         <v>1</v>
       </c>
       <c r="E17" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="29" t="s">
         <v>88</v>
-      </c>
-      <c r="G17" s="29" t="s">
-        <v>89</v>
       </c>
       <c r="H17" s="22"/>
       <c r="I17" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -5037,17 +5036,17 @@
         <v>1</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H18" s="22"/>
       <c r="I18" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -5060,16 +5059,16 @@
         <v>1</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G19" s="3">
         <v>1206</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I19" s="16"/>
     </row>
@@ -5086,7 +5085,7 @@
         <v>33</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G20" s="31" t="s">
         <v>34</v>
@@ -5120,7 +5119,7 @@
         <v>36</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G21" s="3">
         <v>1206</v>
@@ -5129,7 +5128,7 @@
         <v>36</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
@@ -5153,16 +5152,16 @@
         <v>3</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>38</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I22" s="6"/>
       <c r="J22" s="9"/>
@@ -5187,16 +5186,16 @@
         <v>9</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>38</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I23" s="6"/>
       <c r="J23" s="9"/>
@@ -5220,16 +5219,16 @@
         <v>1</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>38</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I24" s="6"/>
       <c r="J24" s="9"/>
@@ -5255,16 +5254,16 @@
         <v>10</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>38</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I25" s="6"/>
       <c r="J25" s="5"/>
@@ -5285,19 +5284,19 @@
         <v>40</v>
       </c>
       <c r="D26" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>38</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I26" s="6"/>
       <c r="J26" s="5"/>
@@ -5321,16 +5320,16 @@
         <v>1</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>38</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I27" s="6"/>
       <c r="J27" s="5"/>
@@ -5351,19 +5350,19 @@
         <v>43</v>
       </c>
       <c r="D28" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I28" s="6"/>
       <c r="J28" s="5"/>
@@ -5378,6 +5377,7 @@
       <c r="S28" s="5"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
         <v>46</v>
@@ -5386,16 +5386,16 @@
         <v>1</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>38</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I29" s="6"/>
       <c r="J29" s="5"/>
@@ -5409,160 +5409,161 @@
       <c r="R29" s="5"/>
       <c r="S29" s="5"/>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D30" s="1">
-        <v>1</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>106</v>
+        <v>63</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E30" s="28" t="s">
+        <v>103</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="I30" s="6"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
-      <c r="Q30" s="5"/>
-      <c r="R30" s="5"/>
-      <c r="S30" s="5"/>
+        <v>75</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I30" s="15"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
     </row>
-    <row r="31" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E31" s="28" t="s">
-        <v>104</v>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C31" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" s="27" t="s">
+        <v>101</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G31" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H31" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I31" s="15"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="3"/>
-      <c r="S31" s="3"/>
+      <c r="H31" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="I31" s="14"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="4"/>
+      <c r="R31" s="4"/>
+      <c r="S31" s="4"/>
+      <c r="T31" s="4"/>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G32" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E32" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="H32" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="I32" s="14"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="4"/>
-      <c r="S32" s="4"/>
+        <v>130</v>
+      </c>
+      <c r="I32" s="21"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
       <c r="T32" s="4"/>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
       <c r="C33" s="26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E33" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="I33" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="I33" s="21"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="7"/>
-      <c r="R33" s="7"/>
-      <c r="S33" s="7"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="4"/>
+      <c r="S33" s="4"/>
       <c r="T33" s="4"/>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="26" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="E34" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>52</v>
+        <v>75</v>
+      </c>
+      <c r="G34" s="7">
+        <v>1812</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="I34" s="21" t="s">
-        <v>135</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="I34" s="14"/>
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -5574,42 +5575,32 @@
       <c r="R34" s="4"/>
       <c r="S34" s="4"/>
       <c r="T34" s="4"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E35" s="27" t="s">
-        <v>98</v>
+        <v>59</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G35" s="7">
-        <v>1812</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="I35" s="14"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="4"/>
-      <c r="S35" s="4"/>
-      <c r="T35" s="4"/>
+        <v>75</v>
+      </c>
+      <c r="G35" s="1">
+        <v>603</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I35" s="16"/>
       <c r="U35" s="2"/>
-      <c r="V35" s="2"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
@@ -5617,113 +5608,110 @@
       <c r="C36" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>96</v>
+      <c r="D36" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E36" s="27" t="s">
+        <v>93</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G36" s="1">
-        <v>603</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="I36" s="16"/>
+        <v>75</v>
+      </c>
+      <c r="G36" s="7">
+        <v>1206</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="I36" s="21"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="7"/>
+      <c r="N36" s="7"/>
+      <c r="O36" s="7"/>
+      <c r="P36" s="7"/>
+      <c r="Q36" s="7"/>
+      <c r="R36" s="7"/>
+      <c r="S36" s="7"/>
       <c r="U36" s="2"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="26" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>62</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G37" s="7">
-        <v>1206</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="I37" s="21"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
-      <c r="N37" s="7"/>
-      <c r="O37" s="7"/>
-      <c r="P37" s="7"/>
-      <c r="Q37" s="7"/>
-      <c r="R37" s="7"/>
-      <c r="S37" s="7"/>
+      <c r="G37" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H37" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="I37" s="14"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="4"/>
+      <c r="Q37" s="4"/>
+      <c r="R37" s="4"/>
+      <c r="S37" s="4"/>
       <c r="U37" s="2"/>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
       <c r="C38" s="26" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E38" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H38" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="I38" s="14"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="4"/>
-      <c r="R38" s="4"/>
-      <c r="S38" s="4"/>
+        <v>57</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H38" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="I38" s="6"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
       <c r="U38" s="2"/>
     </row>
-    <row r="39" spans="1:22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="C39" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H39" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="I39" s="6"/>
+      <c r="B39" s="1"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5"/>
@@ -5779,11 +5767,9 @@
       <c r="U41" s="2"/>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
       <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="25"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="24"/>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
@@ -5801,8 +5787,8 @@
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="D43" s="5"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="24"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="25"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
@@ -5835,87 +5821,88 @@
       <c r="Q44" s="5"/>
       <c r="R44" s="5"/>
       <c r="S44" s="5"/>
-      <c r="U44" s="2"/>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="5"/>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5"/>
-      <c r="O45" s="5"/>
-      <c r="P45" s="5"/>
-      <c r="Q45" s="5"/>
-      <c r="R45" s="5"/>
-      <c r="S45" s="5"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="3"/>
+      <c r="Q45" s="3"/>
+      <c r="R45" s="3"/>
+      <c r="S45" s="3"/>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3"/>
-      <c r="O46" s="3"/>
-      <c r="P46" s="3"/>
-      <c r="Q46" s="3"/>
-      <c r="R46" s="3"/>
-      <c r="S46" s="3"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="4"/>
+      <c r="P46" s="4"/>
+      <c r="Q46" s="4"/>
+      <c r="R46" s="4"/>
+      <c r="S46" s="4"/>
+      <c r="T46" s="4"/>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C47" s="4"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4"/>
-      <c r="N47" s="4"/>
-      <c r="O47" s="4"/>
-      <c r="P47" s="4"/>
-      <c r="Q47" s="4"/>
-      <c r="R47" s="4"/>
-      <c r="S47" s="4"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
+      <c r="M47" s="7"/>
+      <c r="N47" s="7"/>
+      <c r="O47" s="7"/>
+      <c r="P47" s="7"/>
+      <c r="Q47" s="7"/>
+      <c r="R47" s="7"/>
+      <c r="S47" s="7"/>
       <c r="T47" s="4"/>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C48" s="4"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
-      <c r="N48" s="7"/>
-      <c r="O48" s="7"/>
-      <c r="P48" s="7"/>
-      <c r="Q48" s="7"/>
-      <c r="R48" s="7"/>
-      <c r="S48" s="7"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="4"/>
+      <c r="R48" s="4"/>
+      <c r="S48" s="4"/>
       <c r="T48" s="4"/>
     </row>
     <row r="49" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
+      <c r="D49" s="7"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
@@ -5932,26 +5919,6 @@
       <c r="R49" s="4"/>
       <c r="S49" s="4"/>
       <c r="T49" s="4"/>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C50" s="4"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="4"/>
-      <c r="P50" s="4"/>
-      <c r="Q50" s="4"/>
-      <c r="R50" s="4"/>
-      <c r="S50" s="4"/>
-      <c r="T50" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PCB/BOM BreaksRGB_PPU.xlsx
+++ b/PCB/BOM BreaksRGB_PPU.xlsx
@@ -5149,7 +5149,7 @@
         <v>37</v>
       </c>
       <c r="D22" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>118</v>
@@ -5350,7 +5350,7 @@
         <v>43</v>
       </c>
       <c r="D28" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>107</v>
